--- a/bangkok-cloudbeds-hotels.xlsx
+++ b/bangkok-cloudbeds-hotels.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="รายชื่อทั้งหมด" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="สรุปตามเขต" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="แบ่งตามดาว" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="แบ่งตามรีวิว" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="แบ่งตามราคา" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="รายชื่อทั้งหมด" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="สรุปตามเขต" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="แบ่งตามดาว" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="แบ่งตามรีวิว" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="แบ่งตามราคา" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'รายชื่อทั้งหมด'!$A$1:$S$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'รายชื่อทั้งหมด'!$A$1:$S$55</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'สรุปตามเขต'!$A$1:$H$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'แบ่งตามดาว'!$A$1:$J$53</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'แบ่งตามรีวิว'!$A$1:$J$53</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'แบ่งตามราคา'!$A$1:$J$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'แบ่งตามดาว'!$A$1:$J$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'แบ่งตามรีวิว'!$A$1:$J$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'แบ่งตามราคา'!$A$1:$J$55</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S53"/>
+  <dimension ref="A1:S55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3201,69 +3201,66 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Yello Rooms Hotel Victory Monument</t>
+          <t>Hostel MovyLodge</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>โรงแรม</t>
+          <t>โฮสเทล/เกสต์เฮาส์</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>02-002-9428</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>info.yellorooms@gmail.com</t>
+          <t>097 745 4545</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.movylodge.com/</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>3-3.5 ดาว</t>
+          <t>≤2.5 ดาว</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K38" t="n">
-        <v>906</v>
+        <v>658</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Kayak</t>
-        </is>
-      </c>
-      <c r="M38" t="n">
-        <v>1500</v>
+          <t>Google</t>
+        </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>801-1,500</t>
+          <t>ไม่มีข้อมูล</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>12 Soi Ratchawithi 9/11, Phaya Thai Rd, Ratchathewi, Bangkok 10400</t>
+          <t>505 Phetchaburi Rd, Khwaeng Thanon Phaya Thai, Ratchathewi, Bangkok 10400, Thailand</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/zMkAEo</t>
+          <t>https://hotels.cloudbeds.com/reservation/LIR7bX</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>ใช้ Cloudbeds อยู่แล้ว (เจอหน้าจองตรงบน Cloudbeds) เปิดรับระบบออนไลน์และจ่ายค่าซอฟต์แวร์อยู่ / ราคา ~1,500 ฿/คืน กลุ่มราคากลาง ตรงกลุ่มเป้าหมาย / อยู่ย่านท่องเที่ยวหลัก (ราชเทวี) แข่งขันสูง ต้องการเครื่องมือช่วยขาย / มีทั้งเบอร์โทรและอีเมล ติดต่อได้ทันที</t>
+          <t>ใช้ Cloudbeds อยู่แล้ว (เจอหน้าจองตรงบน Cloudbeds) เปิดรับระบบออนไลน์และจ่ายค่าซอฟต์แวร์อยู่ / อยู่ย่านท่องเที่ยวหลัก (ราชเทวี) แข่งขันสูง ต้องการเครื่องมือช่วยขาย / มีเว็บไซต์ของตัวเอง ให้ความสำคัญกับการจองตรง / มีเบอร์โทร ติดต่อได้ทันที</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>ย่านอนุสาวรีย์ชัยฯ</t>
+          <t>พบจาก Google Maps (Apify) · Hostel</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3272,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Spenza Hotel</t>
+          <t>Yello Rooms Hotel Victory Monument</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3285,7 +3282,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>02-251-5251</t>
+          <t>02-002-9428</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>info.yellorooms@gmail.com</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -3297,10 +3299,10 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="K39" t="n">
-        <v>1926</v>
+        <v>906</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -3308,34 +3310,31 @@
         </is>
       </c>
       <c r="M39" t="n">
-        <v>910</v>
+        <v>1500</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
           <t>801-1,500</t>
         </is>
       </c>
-      <c r="O39" t="n">
-        <v>94</v>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>88 Soi Phetchaburi 15, Bangkok 10400</t>
+          <t>12 Soi Ratchawithi 9/11, Phaya Thai Rd, Ratchathewi, Bangkok 10400</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/m9POZF</t>
+          <t>https://hotels.cloudbeds.com/reservation/zMkAEo</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>ใช้ Cloudbeds อยู่แล้ว (เจอหน้าจองตรงบน Cloudbeds) เปิดรับระบบออนไลน์และจ่ายค่าซอฟต์แวร์อยู่ / ขนาดใหญ่ 94 ห้อง งานหน้าบ้านและการจองเยอะ / รีวิว 1,926 รายการ แขกเข้าพักต่อเนื่อง ธุรกิจมีรายได้สม่ำเสมอ / ราคา ~910 ฿/คืน กลุ่มราคากลาง ตรงกลุ่มเป้าหมาย / อยู่ย่านท่องเที่ยวหลัก (ราชเทวี) แข่งขันสูง ต้องการเครื่องมือช่วยขาย / มีเบอร์โทร ติดต่อได้ทันที</t>
+          <t>ใช้ Cloudbeds อยู่แล้ว (เจอหน้าจองตรงบน Cloudbeds) เปิดรับระบบออนไลน์และจ่ายค่าซอฟต์แวร์อยู่ / ราคา ~1,500 ฿/คืน กลุ่มราคากลาง ตรงกลุ่มเป้าหมาย / อยู่ย่านท่องเที่ยวหลัก (ราชเทวี) แข่งขันสูง ต้องการเครื่องมือช่วยขาย / มีทั้งเบอร์โทรและอีเมล ติดต่อได้ทันที</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>ใกล้ประตูน้ำ/แพลทินัม</t>
+          <t>ย่านอนุสาวรีย์ชัยฯ</t>
         </is>
       </c>
     </row>
@@ -3347,71 +3346,67 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>The Victory View (adults only)</t>
+          <t>Spenza Hotel</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>โฮสเทล/เกสต์เฮาส์</t>
+          <t>โรงแรม</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>093-860-5914</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>064-742-4561</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>thevictory.hostel@gmail.com</t>
-        </is>
+          <t>02-251-5251</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>3</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>ไม่ระบุ</t>
+          <t>3-3.5 ดาว</t>
         </is>
       </c>
       <c r="J40" t="n">
         <v>8.6</v>
       </c>
       <c r="K40" t="n">
-        <v>619</v>
+        <v>1926</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Trip.com</t>
+          <t>Kayak</t>
         </is>
       </c>
       <c r="M40" t="n">
-        <v>700</v>
+        <v>910</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>≤800</t>
-        </is>
+          <t>801-1,500</t>
+        </is>
+      </c>
+      <c r="O40" t="n">
+        <v>94</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>34/2-3 Soi Ratchawithi 9, Ratchathewi, Bangkok 10400</t>
+          <t>88 Soi Phetchaburi 15, Bangkok 10400</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/en/reservation/QFq9Zv</t>
+          <t>https://hotels.cloudbeds.com/reservation/m9POZF</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>ใช้ Cloudbeds อยู่แล้ว (เจอหน้าจองตรงบน Cloudbeds) เปิดรับระบบออนไลน์และจ่ายค่าซอฟต์แวร์อยู่ / อยู่ย่านท่องเที่ยวหลัก (ราชเทวี) แข่งขันสูง ต้องการเครื่องมือช่วยขาย / มีทั้งเบอร์โทรและอีเมล ติดต่อได้ทันที</t>
+          <t>ใช้ Cloudbeds อยู่แล้ว (เจอหน้าจองตรงบน Cloudbeds) เปิดรับระบบออนไลน์และจ่ายค่าซอฟต์แวร์อยู่ / ขนาดใหญ่ 94 ห้อง งานหน้าบ้านและการจองเยอะ / รีวิว 1,926 รายการ แขกเข้าพักต่อเนื่อง ธุรกิจมีรายได้สม่ำเสมอ / ราคา ~910 ฿/คืน กลุ่มราคากลาง ตรงกลุ่มเป้าหมาย / อยู่ย่านท่องเที่ยวหลัก (ราชเทวี) แข่งขันสูง ต้องการเครื่องมือช่วยขาย / มีเบอร์โทร ติดต่อได้ทันที</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>~570 ม. BTS อนุสาวรีย์ชัยฯ</t>
+          <t>ใกล้ประตูน้ำ/แพลทินัม</t>
         </is>
       </c>
     </row>
@@ -3423,89 +3418,83 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>4M Pratunam Hotel</t>
+          <t>The Victory View (adults only)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>โรงแรม</t>
+          <t>โฮสเทล/เกสต์เฮาส์</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>02-251-5545</t>
+          <t>093-860-5914</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>081-638-1551</t>
+          <t>064-742-4561</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>4mpratunamhotel@gmail.com</t>
-        </is>
-      </c>
-      <c r="H41" t="n">
-        <v>3</v>
+          <t>thevictory.hostel@gmail.com</t>
+        </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3-3.5 ดาว</t>
+          <t>ไม่ระบุ</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="K41" t="n">
-        <v>1190</v>
+        <v>619</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Kayak</t>
+          <t>Trip.com</t>
         </is>
       </c>
       <c r="M41" t="n">
-        <v>760</v>
+        <v>700</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
           <t>≤800</t>
         </is>
       </c>
-      <c r="O41" t="n">
-        <v>25</v>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>45/6-7 Soi Phetchaburi 15, Bangkok 10400</t>
+          <t>34/2-3 Soi Ratchawithi 9, Ratchathewi, Bangkok 10400</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/BJAq9T</t>
+          <t>https://hotels.cloudbeds.com/en/reservation/QFq9Zv</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>ใช้ Cloudbeds อยู่แล้ว (เจอหน้าจองตรงบน Cloudbeds) เปิดรับระบบออนไลน์และจ่ายค่าซอฟต์แวร์อยู่ / ขนาดกลาง 25 ห้อง กำลังโต / รีวิว 1,190 รายการ แขกเข้าพักต่อเนื่อง ธุรกิจมีรายได้สม่ำเสมอ / อยู่ย่านท่องเที่ยวหลัก (ราชเทวี) แข่งขันสูง ต้องการเครื่องมือช่วยขาย / มีทั้งเบอร์โทรและอีเมล ติดต่อได้ทันที</t>
+          <t>ใช้ Cloudbeds อยู่แล้ว (เจอหน้าจองตรงบน Cloudbeds) เปิดรับระบบออนไลน์และจ่ายค่าซอฟต์แวร์อยู่ / อยู่ย่านท่องเที่ยวหลัก (ราชเทวี) แข่งขันสูง ต้องการเครื่องมือช่วยขาย / มีทั้งเบอร์โทรและอีเมล ติดต่อได้ทันที</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>อาหารเช้า 150 บาท</t>
+          <t>~570 ม. BTS อนุสาวรีย์ชัยฯ</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>วัฒนา</t>
+          <t>ราชเทวี</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Sib Kao</t>
+          <t>4M Pratunam Hotel</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3515,12 +3504,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>02-254-3200</t>
+          <t>02-251-5545</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>081-638-1551</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>info@sibkao.com</t>
+          <t>4mpratunamhotel@gmail.com</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -3532,10 +3526,10 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K42" t="n">
-        <v>1082</v>
+        <v>1190</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -3543,31 +3537,34 @@
         </is>
       </c>
       <c r="M42" t="n">
-        <v>1190</v>
+        <v>760</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>801-1,500</t>
-        </is>
+          <t>≤800</t>
+        </is>
+      </c>
+      <c r="O42" t="n">
+        <v>25</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>19/27-28 Sukhumvit Soi 19, Khlong Toei Nuea, Bangkok 10110</t>
+          <t>45/6-7 Soi Phetchaburi 15, Bangkok 10400</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/LCLlYQ</t>
+          <t>https://hotels.cloudbeds.com/reservation/BJAq9T</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>ใช้ Cloudbeds อยู่แล้ว (เจอหน้าจองตรงบน Cloudbeds) เปิดรับระบบออนไลน์และจ่ายค่าซอฟต์แวร์อยู่ / รีวิว 1,082 รายการ แขกเข้าพักต่อเนื่อง ธุรกิจมีรายได้สม่ำเสมอ / คะแนนรีวิว 9.0 ดีเยี่ยม ใส่ใจคุณภาพ พร้อมลงทุนต่อ / ราคา ~1,190 ฿/คืน กลุ่มราคากลาง ตรงกลุ่มเป้าหมาย / อยู่ย่านท่องเที่ยวหลัก (วัฒนา) แข่งขันสูง ต้องการเครื่องมือช่วยขาย / มีทั้งเบอร์โทรและอีเมล ติดต่อได้ทันที</t>
+          <t>ใช้ Cloudbeds อยู่แล้ว (เจอหน้าจองตรงบน Cloudbeds) เปิดรับระบบออนไลน์และจ่ายค่าซอฟต์แวร์อยู่ / ขนาดกลาง 25 ห้อง กำลังโต / รีวิว 1,190 รายการ แขกเข้าพักต่อเนื่อง ธุรกิจมีรายได้สม่ำเสมอ / อยู่ย่านท่องเที่ยวหลัก (ราชเทวี) แข่งขันสูง ต้องการเครื่องมือช่วยขาย / มีทั้งเบอร์โทรและอีเมล ติดต่อได้ทันที</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>ใกล้ Terminal 21</t>
+          <t>อาหารเช้า 150 บาท</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3576,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>StayAt Bedever Bangkok Hotel</t>
+          <t>Met A Space Pod @Phrom Phong</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>บูทีค</t>
+          <t>โฮสเทล/เกสต์เฮาส์</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>084 689 2264</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>http://metaspacepod.com.sg/</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3593,45 +3600,39 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K43" t="n">
-        <v>61</v>
+        <v>252</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Expedia</t>
-        </is>
-      </c>
-      <c r="M43" t="n">
-        <v>730</v>
+          <t>Google</t>
+        </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>≤800</t>
-        </is>
-      </c>
-      <c r="O43" t="n">
-        <v>21</v>
+          <t>ไม่มีข้อมูล</t>
+        </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>1533/3-4 Sukhumvit Rd, Phra Khanong Nuea, Bangkok 10110</t>
+          <t>24/4 Sukhumvit 35 Alley, Khwaeng Khlong Tan Nuea, Watthana, Bangkok 10110, Thailand</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>https://us2.cloudbeds.com/reservation/z3rPaG</t>
+          <t>https://hotels.cloudbeds.com/reservation/rXdLyg</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>ใช้ Cloudbeds อยู่แล้ว (เจอหน้าจองตรงบน Cloudbeds) เปิดรับระบบออนไลน์และจ่ายค่าซอฟต์แวร์อยู่ / ขนาดกลาง 21 ห้อง กำลังโต / อยู่ย่านท่องเที่ยวหลัก (วัฒนา) แข่งขันสูง ต้องการเครื่องมือช่วยขาย</t>
+          <t>ใช้ Cloudbeds อยู่แล้ว (เจอหน้าจองตรงบน Cloudbeds) เปิดรับระบบออนไลน์และจ่ายค่าซอฟต์แวร์อยู่ / คะแนนรีวิว 9.2 ดีเยี่ยม ใส่ใจคุณภาพ พร้อมลงทุนต่อ / อยู่ย่านท่องเที่ยวหลัก (วัฒนา) แข่งขันสูง ต้องการเครื่องมือช่วยขาย / มีเว็บไซต์ของตัวเอง ให้ความสำคัญกับการจองตรง / มีเบอร์โทร ติดต่อได้ทันที</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>ใช้ Cloudbeds โดเมน us2.cloudbeds.com</t>
+          <t>พบจาก Google Maps (Apify) · Hostel</t>
         </is>
       </c>
     </row>
@@ -3643,73 +3644,69 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Lamurr Sukhumvit 41</t>
+          <t>Sib Kao</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>โฮสเทล/เกสต์เฮาส์</t>
+          <t>โรงแรม</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>02-040-4653</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>097-140-5544</t>
+          <t>02-254-3200</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>info@lamurr.com</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>https://lamurr.com</t>
-        </is>
+          <t>info@sibkao.com</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>3</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>ไม่ระบุ</t>
+          <t>3-3.5 ดาว</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="K44" t="n">
-        <v>1129</v>
+        <v>1082</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>Kayak</t>
         </is>
       </c>
+      <c r="M44" t="n">
+        <v>1190</v>
+      </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>ไม่มีข้อมูล</t>
+          <t>801-1,500</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sukhumvit Soi 41, Khlong Tan Nuea, Bangkok 10110</t>
+          <t>19/27-28 Sukhumvit Soi 19, Khlong Toei Nuea, Bangkok 10110</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/dBVH5M</t>
+          <t>https://hotels.cloudbeds.com/reservation/LCLlYQ</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>ใช้ Cloudbeds อยู่แล้ว (เจอหน้าจองตรงบน Cloudbeds) เปิดรับระบบออนไลน์และจ่ายค่าซอฟต์แวร์อยู่ / รีวิว 1,129 รายการ แขกเข้าพักต่อเนื่อง ธุรกิจมีรายได้สม่ำเสมอ / อยู่ย่านท่องเที่ยวหลัก (วัฒนา) แข่งขันสูง ต้องการเครื่องมือช่วยขาย / มีเว็บไซต์ของตัวเอง ให้ความสำคัญกับการจองตรง / มีทั้งเบอร์โทรและอีเมล ติดต่อได้ทันที</t>
+          <t>ใช้ Cloudbeds อยู่แล้ว (เจอหน้าจองตรงบน Cloudbeds) เปิดรับระบบออนไลน์และจ่ายค่าซอฟต์แวร์อยู่ / รีวิว 1,082 รายการ แขกเข้าพักต่อเนื่อง ธุรกิจมีรายได้สม่ำเสมอ / คะแนนรีวิว 9.0 ดีเยี่ยม ใส่ใจคุณภาพ พร้อมลงทุนต่อ / ราคา ~1,190 ฿/คืน กลุ่มราคากลาง ตรงกลุ่มเป้าหมาย / อยู่ย่านท่องเที่ยวหลัก (วัฒนา) แข่งขันสูง ต้องการเครื่องมือช่วยขาย / มีทั้งเบอร์โทรและอีเมล ติดต่อได้ทันที</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>ใกล้ BTS พร้อมพงษ์</t>
+          <t>ใกล้ Terminal 21</t>
         </is>
       </c>
     </row>
@@ -3721,64 +3718,59 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>W 21 Hotel Bangkok</t>
+          <t>StayAt Bedever Bangkok Hotel</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>โรงแรม</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>02-661-6200</t>
-        </is>
-      </c>
-      <c r="H45" t="n">
-        <v>3</v>
+          <t>บูทีค</t>
+        </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>3-3.5 ดาว</t>
+          <t>ไม่ระบุ</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K45" t="n">
-        <v>1548</v>
+        <v>61</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Kayak</t>
+          <t>Expedia</t>
         </is>
       </c>
       <c r="M45" t="n">
-        <v>1020</v>
+        <v>730</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>801-1,500</t>
-        </is>
+          <t>≤800</t>
+        </is>
+      </c>
+      <c r="O45" t="n">
+        <v>21</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>4/56 Asok Montri Rd (Sukhumvit 21), Khlong Toei Nuea, Bangkok 10110</t>
+          <t>1533/3-4 Sukhumvit Rd, Phra Khanong Nuea, Bangkok 10110</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/3pn5ml</t>
+          <t>https://us2.cloudbeds.com/reservation/z3rPaG</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>ใช้ Cloudbeds อยู่แล้ว (เจอหน้าจองตรงบน Cloudbeds) เปิดรับระบบออนไลน์และจ่ายค่าซอฟต์แวร์อยู่ / รีวิว 1,548 รายการ แขกเข้าพักต่อเนื่อง ธุรกิจมีรายได้สม่ำเสมอ / ราคา ~1,020 ฿/คืน กลุ่มราคากลาง ตรงกลุ่มเป้าหมาย / อยู่ย่านท่องเที่ยวหลัก (วัฒนา) แข่งขันสูง ต้องการเครื่องมือช่วยขาย / มีเบอร์โทร ติดต่อได้ทันที</t>
+          <t>ใช้ Cloudbeds อยู่แล้ว (เจอหน้าจองตรงบน Cloudbeds) เปิดรับระบบออนไลน์และจ่ายค่าซอฟต์แวร์อยู่ / ขนาดกลาง 21 ห้อง กำลังโต / อยู่ย่านท่องเที่ยวหลัก (วัฒนา) แข่งขันสูง ต้องการเครื่องมือช่วยขาย</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>ชื่อเดิม Serene Asoke Suites</t>
+          <t>ใช้ Cloudbeds โดเมน us2.cloudbeds.com</t>
         </is>
       </c>
     </row>
@@ -3790,7 +3782,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>3Howw Hostel @ Sukhumvit 21</t>
+          <t>Lamurr Sukhumvit 41</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3800,12 +3792,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>099-909-6997</t>
+          <t>02-040-4653</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>097-140-5544</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>3howw.sukhumvit21@gmail.com</t>
+          <t>info@lamurr.com</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>https://lamurr.com</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3814,10 +3816,10 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>7.7</v>
+        <v>8.4</v>
       </c>
       <c r="K46" t="n">
-        <v>2741</v>
+        <v>1129</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -3831,22 +3833,22 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>32/9 Sukhumvit 21 Soi 1, Bangkok 10110</t>
+          <t>Sukhumvit Soi 41, Khlong Tan Nuea, Bangkok 10110</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/jABe3g</t>
+          <t>https://hotels.cloudbeds.com/reservation/dBVH5M</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>ใช้ Cloudbeds อยู่แล้ว (เจอหน้าจองตรงบน Cloudbeds) เปิดรับระบบออนไลน์และจ่ายค่าซอฟต์แวร์อยู่ / รีวิว 2,741 รายการ แขกเข้าพักต่อเนื่อง ธุรกิจมีรายได้สม่ำเสมอ / อยู่ย่านท่องเที่ยวหลัก (วัฒนา) แข่งขันสูง ต้องการเครื่องมือช่วยขาย / มีทั้งเบอร์โทรและอีเมล ติดต่อได้ทันที</t>
+          <t>ใช้ Cloudbeds อยู่แล้ว (เจอหน้าจองตรงบน Cloudbeds) เปิดรับระบบออนไลน์และจ่ายค่าซอฟต์แวร์อยู่ / รีวิว 1,129 รายการ แขกเข้าพักต่อเนื่อง ธุรกิจมีรายได้สม่ำเสมอ / อยู่ย่านท่องเที่ยวหลัก (วัฒนา) แข่งขันสูง ต้องการเครื่องมือช่วยขาย / มีเว็บไซต์ของตัวเอง ให้ความสำคัญกับการจองตรง / มีทั้งเบอร์โทรและอีเมล ติดต่อได้ทันที</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>เดิน 5 นาที BTS อโศก</t>
+          <t>ใกล้ BTS พร้อมพงษ์</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3860,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Sakura Sky Residence</t>
+          <t>W 21 Hotel Bangkok</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3868,7 +3870,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>02-259-5999</t>
+          <t>02-661-6200</t>
         </is>
       </c>
       <c r="H47" t="n">
@@ -3880,18 +3882,18 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="K47" t="n">
-        <v>412</v>
+        <v>1548</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Expedia</t>
+          <t>Kayak</t>
         </is>
       </c>
       <c r="M47" t="n">
-        <v>920</v>
+        <v>1020</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
@@ -3900,22 +3902,22 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>9/1 Sukhumvit 33, Khlong Tan Nuea, Bangkok 10110</t>
+          <t>4/56 Asok Montri Rd (Sukhumvit 21), Khlong Toei Nuea, Bangkok 10110</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/519d0O</t>
+          <t>https://hotels.cloudbeds.com/reservation/3pn5ml</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>ใช้ Cloudbeds อยู่แล้ว (เจอหน้าจองตรงบน Cloudbeds) เปิดรับระบบออนไลน์และจ่ายค่าซอฟต์แวร์อยู่ / ราคา ~920 ฿/คืน กลุ่มราคากลาง ตรงกลุ่มเป้าหมาย / อยู่ย่านท่องเที่ยวหลัก (วัฒนา) แข่งขันสูง ต้องการเครื่องมือช่วยขาย / มีเบอร์โทร ติดต่อได้ทันที</t>
+          <t>ใช้ Cloudbeds อยู่แล้ว (เจอหน้าจองตรงบน Cloudbeds) เปิดรับระบบออนไลน์และจ่ายค่าซอฟต์แวร์อยู่ / รีวิว 1,548 รายการ แขกเข้าพักต่อเนื่อง ธุรกิจมีรายได้สม่ำเสมอ / ราคา ~1,020 ฿/คืน กลุ่มราคากลาง ตรงกลุ่มเป้าหมาย / อยู่ย่านท่องเที่ยวหลัก (วัฒนา) แข่งขันสูง ต้องการเครื่องมือช่วยขาย / มีเบอร์โทร ติดต่อได้ทันที</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>เดิน 7 นาที BTS พร้อมพงษ์</t>
+          <t>ชื่อเดิม Serene Asoke Suites</t>
         </is>
       </c>
     </row>
@@ -3927,74 +3929,63 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Thonglor Suites Hotel</t>
+          <t>3Howw Hostel @ Sukhumvit 21</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>โรงแรม</t>
+          <t>โฮสเทล/เกสต์เฮาส์</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>02-001-2698</t>
+          <t>099-909-6997</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>info@thonglorsuites.com</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>https://thonglorsuites.com</t>
-        </is>
-      </c>
-      <c r="H48" t="n">
-        <v>2.5</v>
+          <t>3howw.sukhumvit21@gmail.com</t>
+        </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>≤2.5 ดาว</t>
+          <t>ไม่ระบุ</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>6.4</v>
+        <v>7.7</v>
       </c>
       <c r="K48" t="n">
-        <v>73</v>
+        <v>2741</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Trip.com</t>
-        </is>
-      </c>
-      <c r="M48" t="n">
-        <v>920</v>
+          <t>Kayak</t>
+        </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>801-1,500</t>
+          <t>ไม่มีข้อมูล</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2/7 Soi Sukhumvit 53, Khlong Tan Nuea, Bangkok 10110</t>
+          <t>32/9 Sukhumvit 21 Soi 1, Bangkok 10110</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/tN3wfD</t>
+          <t>https://hotels.cloudbeds.com/reservation/jABe3g</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>ใช้ Cloudbeds อยู่แล้ว (เจอหน้าจองตรงบน Cloudbeds) เปิดรับระบบออนไลน์และจ่ายค่าซอฟต์แวร์อยู่ / คะแนนรีวิว 6.4 ค่อนข้างต่ำ มีจุดให้ช่วยปรับปรุงบริการ / ราคา ~920 ฿/คืน กลุ่มราคากลาง ตรงกลุ่มเป้าหมาย / อยู่ย่านท่องเที่ยวหลัก (วัฒนา) แข่งขันสูง ต้องการเครื่องมือช่วยขาย / มีเว็บไซต์ของตัวเอง ให้ความสำคัญกับการจองตรง / มีทั้งเบอร์โทรและอีเมล ติดต่อได้ทันที</t>
+          <t>ใช้ Cloudbeds อยู่แล้ว (เจอหน้าจองตรงบน Cloudbeds) เปิดรับระบบออนไลน์และจ่ายค่าซอฟต์แวร์อยู่ / รีวิว 2,741 รายการ แขกเข้าพักต่อเนื่อง ธุรกิจมีรายได้สม่ำเสมอ / อยู่ย่านท่องเที่ยวหลัก (วัฒนา) แข่งขันสูง ต้องการเครื่องมือช่วยขาย / มีทั้งเบอร์โทรและอีเมล ติดต่อได้ทันที</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>ไม่มีลิฟต์ · 50 ม. BTS ทองหล่อ</t>
+          <t>เดิน 5 นาที BTS อโศก</t>
         </is>
       </c>
     </row>
@@ -4006,84 +3997,100 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Narastay @ Phrom Phong</t>
+          <t>Sakura Sky Residence</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>เซอร์วิส อพาร์ตเมนต์</t>
+          <t>โรงแรม</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>062-818-1865</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>booking@narastay.com</t>
-        </is>
+          <t>02-259-5999</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>3</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>ไม่ระบุ</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr"/>
+          <t>3-3.5 ดาว</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="K49" t="n">
+        <v>412</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Expedia</t>
+        </is>
+      </c>
+      <c r="M49" t="n">
+        <v>920</v>
+      </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>ไม่มีข้อมูล</t>
+          <t>801-1,500</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>51/4 Sukhumvit Soi 39, Bangkok 10110</t>
+          <t>9/1 Sukhumvit 33, Khlong Tan Nuea, Bangkok 10110</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/mQ8KAh</t>
+          <t>https://hotels.cloudbeds.com/reservation/519d0O</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>ใช้ Cloudbeds อยู่แล้ว (เจอหน้าจองตรงบน Cloudbeds) เปิดรับระบบออนไลน์และจ่ายค่าซอฟต์แวร์อยู่ / อยู่ย่านท่องเที่ยวหลัก (วัฒนา) แข่งขันสูง ต้องการเครื่องมือช่วยขาย / มีทั้งเบอร์โทรและอีเมล ติดต่อได้ทันที</t>
+          <t>ใช้ Cloudbeds อยู่แล้ว (เจอหน้าจองตรงบน Cloudbeds) เปิดรับระบบออนไลน์และจ่ายค่าซอฟต์แวร์อยู่ / ราคา ~920 ฿/คืน กลุ่มราคากลาง ตรงกลุ่มเป้าหมาย / อยู่ย่านท่องเที่ยวหลัก (วัฒนา) แข่งขันสูง ต้องการเครื่องมือช่วยขาย / มีเบอร์โทร ติดต่อได้ทันที</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>น่าจะเปิดใหม่ ยังไม่มีรีวิว</t>
+          <t>เดิน 7 นาที BTS พร้อมพงษ์</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>สัมพันธวงศ์</t>
+          <t>วัฒนา</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tiny Taladnoi Hostel</t>
+          <t>Thonglor Suites Hotel</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>โฮสเทล/เกสต์เฮาส์</t>
+          <t>โรงแรม</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>02-048-8515</t>
+          <t>02-001-2698</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>info.tinytaladnoi@gmail.com</t>
+          <t>info@thonglorsuites.com</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>https://thonglorsuites.com</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -4091,69 +4098,69 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>9.300000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="K50" t="n">
-        <v>565</v>
+        <v>73</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Trabber</t>
+          <t>Trip.com</t>
         </is>
       </c>
       <c r="M50" t="n">
-        <v>600</v>
+        <v>920</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>≤800</t>
+          <t>801-1,500</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>80-82 Yotha Rd, Talat Noi, Samphanthawong, Bangkok 10100</t>
+          <t>2/7 Soi Sukhumvit 53, Khlong Tan Nuea, Bangkok 10110</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/hveMzn</t>
+          <t>https://hotels.cloudbeds.com/reservation/tN3wfD</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>ใช้ Cloudbeds อยู่แล้ว (เจอหน้าจองตรงบน Cloudbeds) เปิดรับระบบออนไลน์และจ่ายค่าซอฟต์แวร์อยู่ / คะแนนรีวิว 9.3 ดีเยี่ยม ใส่ใจคุณภาพ พร้อมลงทุนต่อ / อยู่ย่านท่องเที่ยวหลัก (สัมพันธวงศ์) แข่งขันสูง ต้องการเครื่องมือช่วยขาย / มีทั้งเบอร์โทรและอีเมล ติดต่อได้ทันที</t>
+          <t>ใช้ Cloudbeds อยู่แล้ว (เจอหน้าจองตรงบน Cloudbeds) เปิดรับระบบออนไลน์และจ่ายค่าซอฟต์แวร์อยู่ / คะแนนรีวิว 6.4 ค่อนข้างต่ำ มีจุดให้ช่วยปรับปรุงบริการ / ราคา ~920 ฿/คืน กลุ่มราคากลาง ตรงกลุ่มเป้าหมาย / อยู่ย่านท่องเที่ยวหลัก (วัฒนา) แข่งขันสูง ต้องการเครื่องมือช่วยขาย / มีเว็บไซต์ของตัวเอง ให้ความสำคัญกับการจองตรง / มีทั้งเบอร์โทรและอีเมล ติดต่อได้ทันที</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>ใกล้ River City</t>
+          <t>ไม่มีลิฟต์ · 50 ม. BTS ทองหล่อ</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>สัมพันธวงศ์</t>
+          <t>วัฒนา</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Luk Hostel</t>
+          <t>Narastay @ Phrom Phong</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>โฮสเทล/เกสต์เฮาส์</t>
+          <t>เซอร์วิส อพาร์ตเมนต์</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>092-280-3385</t>
+          <t>062-818-1865</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>lukandrise@gmail.com</t>
+          <t>booking@narastay.com</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -4161,201 +4168,333 @@
           <t>ไม่ระบุ</t>
         </is>
       </c>
-      <c r="J51" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="K51" t="n">
-        <v>1774</v>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>HotelsCombined</t>
-        </is>
-      </c>
-      <c r="M51" t="n">
-        <v>880</v>
-      </c>
+      <c r="L51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>801-1,500</t>
+          <t>ไม่มีข้อมูล</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>382-386 Vanich 1 Rd, Samphanthawong, Bangkok 10100</t>
+          <t>51/4 Sukhumvit Soi 39, Bangkok 10110</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/HlTUl3</t>
+          <t>https://hotels.cloudbeds.com/reservation/mQ8KAh</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>ใช้ Cloudbeds อยู่แล้ว (เจอหน้าจองตรงบน Cloudbeds) เปิดรับระบบออนไลน์และจ่ายค่าซอฟต์แวร์อยู่ / รีวิว 1,774 รายการ แขกเข้าพักต่อเนื่อง ธุรกิจมีรายได้สม่ำเสมอ / ราคา ~880 ฿/คืน กลุ่มราคากลาง ตรงกลุ่มเป้าหมาย / อยู่ย่านท่องเที่ยวหลัก (สัมพันธวงศ์) แข่งขันสูง ต้องการเครื่องมือช่วยขาย / มีทั้งเบอร์โทรและอีเมล ติดต่อได้ทันที</t>
+          <t>ใช้ Cloudbeds อยู่แล้ว (เจอหน้าจองตรงบน Cloudbeds) เปิดรับระบบออนไลน์และจ่ายค่าซอฟต์แวร์อยู่ / อยู่ย่านท่องเที่ยวหลัก (วัฒนา) แข่งขันสูง ต้องการเครื่องมือช่วยขาย / มีทั้งเบอร์โทรและอีเมล ติดต่อได้ทันที</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>เยาวราช · รับเงินสดเท่านั้น</t>
+          <t>น่าจะเปิดใหม่ ยังไม่มีรีวิว</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>สาทร</t>
+          <t>สัมพันธวงศ์</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Jasaen Stylish Boutique Hotel</t>
+          <t>Tiny Taladnoi Hostel</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>บูทีค</t>
+          <t>โฮสเทล/เกสต์เฮาส์</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>02-675-9198</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>094-482-0085</t>
+          <t>02-048-8515</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>baanpraya.booking@gmail.com</t>
-        </is>
+          <t>info.tinytaladnoi@gmail.com</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>2</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>ไม่ระบุ</t>
+          <t>≤2.5 ดาว</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>8.300000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>840</v>
+        <v>565</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Kayak</t>
-        </is>
+          <t>Trabber</t>
+        </is>
+      </c>
+      <c r="M52" t="n">
+        <v>600</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>ไม่มีข้อมูล</t>
-        </is>
-      </c>
-      <c r="O52" t="n">
-        <v>32</v>
+          <t>≤800</t>
+        </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>168 Soi Charoen Krung 57, Yannawa, Sathon, Bangkok 10120</t>
+          <t>80-82 Yotha Rd, Talat Noi, Samphanthawong, Bangkok 10100</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/JXh4be</t>
+          <t>https://hotels.cloudbeds.com/reservation/hveMzn</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>ใช้ Cloudbeds อยู่แล้ว (เจอหน้าจองตรงบน Cloudbeds) เปิดรับระบบออนไลน์และจ่ายค่าซอฟต์แวร์อยู่ / ขนาดกลาง 32 ห้อง กำลังโต / อยู่ย่านท่องเที่ยวหลัก (สาทร) แข่งขันสูง ต้องการเครื่องมือช่วยขาย / มีทั้งเบอร์โทรและอีเมล ติดต่อได้ทันที</t>
+          <t>ใช้ Cloudbeds อยู่แล้ว (เจอหน้าจองตรงบน Cloudbeds) เปิดรับระบบออนไลน์และจ่ายค่าซอฟต์แวร์อยู่ / คะแนนรีวิว 9.3 ดีเยี่ยม ใส่ใจคุณภาพ พร้อมลงทุนต่อ / อยู่ย่านท่องเที่ยวหลัก (สัมพันธวงศ์) แข่งขันสูง ต้องการเครื่องมือช่วยขาย / มีทั้งเบอร์โทรและอีเมล ติดต่อได้ทันที</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>ตึกแถวเก่า 7 คูหา · ใกล้ BTS สะพานตากสิน</t>
+          <t>ใกล้ River City</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>สัมพันธวงศ์</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Luk Hostel</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>โฮสเทล/เกสต์เฮาส์</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>092-280-3385</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>lukandrise@gmail.com</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="K53" t="n">
+        <v>1774</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>HotelsCombined</t>
+        </is>
+      </c>
+      <c r="M53" t="n">
+        <v>880</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>801-1,500</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>382-386 Vanich 1 Rd, Samphanthawong, Bangkok 10100</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>https://hotels.cloudbeds.com/reservation/HlTUl3</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>ใช้ Cloudbeds อยู่แล้ว (เจอหน้าจองตรงบน Cloudbeds) เปิดรับระบบออนไลน์และจ่ายค่าซอฟต์แวร์อยู่ / รีวิว 1,774 รายการ แขกเข้าพักต่อเนื่อง ธุรกิจมีรายได้สม่ำเสมอ / ราคา ~880 ฿/คืน กลุ่มราคากลาง ตรงกลุ่มเป้าหมาย / อยู่ย่านท่องเที่ยวหลัก (สัมพันธวงศ์) แข่งขันสูง ต้องการเครื่องมือช่วยขาย / มีทั้งเบอร์โทรและอีเมล ติดต่อได้ทันที</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>เยาวราช · รับเงินสดเท่านั้น</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>สาทร</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Jasaen Stylish Boutique Hotel</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>บูทีค</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>02-675-9198</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>094-482-0085</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>baanpraya.booking@gmail.com</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="K54" t="n">
+        <v>840</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Kayak</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>ไม่มีข้อมูล</t>
+        </is>
+      </c>
+      <c r="O54" t="n">
+        <v>32</v>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>168 Soi Charoen Krung 57, Yannawa, Sathon, Bangkok 10120</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>https://hotels.cloudbeds.com/reservation/JXh4be</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>ใช้ Cloudbeds อยู่แล้ว (เจอหน้าจองตรงบน Cloudbeds) เปิดรับระบบออนไลน์และจ่ายค่าซอฟต์แวร์อยู่ / ขนาดกลาง 32 ห้อง กำลังโต / อยู่ย่านท่องเที่ยวหลัก (สาทร) แข่งขันสูง ต้องการเครื่องมือช่วยขาย / มีทั้งเบอร์โทรและอีเมล ติดต่อได้ทันที</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>ตึกแถวเก่า 7 คูหา · ใกล้ BTS สะพานตากสิน</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>สาทร</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
         <is>
           <t>Urbana Sathorn</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>เซอร์วิส อพาร์ตเมนต์</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>02-227-9999</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>rsvn@urbanasathorn.com</t>
         </is>
       </c>
-      <c r="H53" t="n">
+      <c r="H55" t="n">
         <v>5</v>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>4-5 ดาว</t>
         </is>
       </c>
-      <c r="J53" t="n">
+      <c r="J55" t="n">
         <v>8</v>
       </c>
-      <c r="K53" t="n">
+      <c r="K55" t="n">
         <v>4554</v>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>Kayak</t>
         </is>
       </c>
-      <c r="M53" t="n">
+      <c r="M55" t="n">
         <v>1900</v>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>1,501-2,500</t>
         </is>
       </c>
-      <c r="O53" t="n">
+      <c r="O55" t="n">
         <v>156</v>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>South Sathorn Rd, Bangkok</t>
         </is>
       </c>
-      <c r="Q53" s="2" t="inlineStr">
+      <c r="Q55" s="2" t="inlineStr">
         <is>
           <t>https://hotels.cloudbeds.com/reservation/kXbLpy</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr">
+      <c r="R55" t="inlineStr">
         <is>
           <t>ใช้ Cloudbeds อยู่แล้ว (เจอหน้าจองตรงบน Cloudbeds) เปิดรับระบบออนไลน์และจ่ายค่าซอฟต์แวร์อยู่ / ขนาดใหญ่ 156 ห้อง งานหน้าบ้านและการจองเยอะ / ระดับ 5 ดาว มีงบลงทุนระบบ / รีวิว 4,554 รายการ แขกเข้าพักต่อเนื่อง ธุรกิจมีรายได้สม่ำเสมอ / ราคา ~1,900 ฿/คืน กลุ่มราคากลาง ตรงกลุ่มเป้าหมาย / อยู่ย่านท่องเที่ยวหลัก (สาทร) แข่งขันสูง ต้องการเครื่องมือช่วยขาย / มีทั้งเบอร์โทรและอีเมล ติดต่อได้ทันที</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
+      <c r="S55" t="inlineStr">
         <is>
           <t>ดาวประกาศเองบนหน้าจอง ยังไม่ยืนยัน · ห้องมีครัว</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S53"/>
+  <autoFilter ref="A1:S55"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
@@ -4404,24 +4543,28 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q36" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q37" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q38" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q39" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q40" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q41" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q42" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q43" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q44" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q45" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q46" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q47" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q48" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q49" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q50" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q51" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q52" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q53" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q38" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q39" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q40" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q41" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q42" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q43" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q44" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q45" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q46" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q47" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q48" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q49" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q50" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q51" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q52" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q53" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q54" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q55" r:id="rId69"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4523,19 +4666,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
         <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F3" t="n">
-        <v>7.96</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>730</v>
@@ -4547,35 +4690,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>บางรัก</t>
+          <t>ราชเทวี</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4" t="n">
-        <v>8.67</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>460</v>
+        <v>700</v>
       </c>
       <c r="H4" t="n">
-        <v>2500</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ราชเทวี</t>
+          <t>บางรัก</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -4591,13 +4734,13 @@
         <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>8.58</v>
+        <v>8.67</v>
       </c>
       <c r="G5" t="n">
-        <v>700</v>
+        <v>460</v>
       </c>
       <c r="H5" t="n">
-        <v>1500</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="6">
@@ -4853,16 +4996,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C15" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D15" t="n">
         <v>27</v>
       </c>
       <c r="E15" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -4877,7 +5020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5776,39 +5919,36 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>วัฒนา</t>
+          <t>ราชเทวี</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Thonglor Suites Hotel</t>
+          <t>Hostel MovyLodge</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>โรงแรม</t>
+          <t>โฮสเทล/เกสต์เฮาส์</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>02-001-2698</t>
+          <t>097 745 4545</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="G21" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>73</v>
-      </c>
-      <c r="I21" t="n">
-        <v>920</v>
+        <v>658</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/tN3wfD</t>
+          <t>https://hotels.cloudbeds.com/reservation/LIR7bX</t>
         </is>
       </c>
     </row>
@@ -5820,56 +5960,56 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>สัมพันธวงศ์</t>
+          <t>วัฒนา</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tiny Taladnoi Hostel</t>
+          <t>Thonglor Suites Hotel</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>โฮสเทล/เกสต์เฮาส์</t>
+          <t>โรงแรม</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>02-048-8515</t>
+          <t>02-001-2698</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="G22" t="n">
-        <v>9.300000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="H22" t="n">
-        <v>565</v>
+        <v>73</v>
       </c>
       <c r="I22" t="n">
-        <v>600</v>
+        <v>920</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/hveMzn</t>
+          <t>https://hotels.cloudbeds.com/reservation/tN3wfD</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ไม่ระบุ</t>
+          <t>≤2.5 ดาว</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>จตุจักร</t>
+          <t>สัมพันธวงศ์</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bed to Bangkok</t>
+          <t>Tiny Taladnoi Hostel</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -5879,18 +6019,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>082-210-0268</t>
-        </is>
+          <t>02-048-8515</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>2</v>
       </c>
       <c r="G23" t="n">
-        <v>7.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>226</v>
+        <v>565</v>
+      </c>
+      <c r="I23" t="n">
+        <v>600</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/13e7WW</t>
+          <t>https://hotels.cloudbeds.com/reservation/hveMzn</t>
         </is>
       </c>
     </row>
@@ -5902,12 +6048,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ดอนเมือง</t>
+          <t>จตุจักร</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sloth Hostel DonMueang Airport</t>
+          <t>Bed to Bangkok</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5917,18 +6063,18 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>082-251-7889</t>
+          <t>082-210-0268</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>9</v>
+        <v>7.9</v>
       </c>
       <c r="H24" t="n">
-        <v>689</v>
+        <v>226</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/zGqPFy</t>
+          <t>https://hotels.cloudbeds.com/reservation/13e7WW</t>
         </is>
       </c>
     </row>
@@ -5940,12 +6086,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>บางรัก</t>
+          <t>ดอนเมือง</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BRB Hostel Bangkok Silom</t>
+          <t>Sloth Hostel DonMueang Airport</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5955,21 +6101,18 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>061-515-9898</t>
+          <t>082-251-7889</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="H25" t="n">
-        <v>1420</v>
-      </c>
-      <c r="I25" t="n">
-        <v>460</v>
+        <v>689</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/vhyeOS</t>
+          <t>https://hotels.cloudbeds.com/reservation/zGqPFy</t>
         </is>
       </c>
     </row>
@@ -5986,7 +6129,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CLOUD on Saladaeng Hostel</t>
+          <t>BRB Hostel Bangkok Silom</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5996,18 +6139,21 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>02-029-9729</t>
+          <t>061-515-9898</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>9</v>
+        <v>7.8</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1420</v>
       </c>
       <c r="I26" t="n">
-        <v>1120</v>
+        <v>460</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/iGlZHg</t>
+          <t>https://hotels.cloudbeds.com/reservation/vhyeOS</t>
         </is>
       </c>
     </row>
@@ -6024,31 +6170,28 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pas Cher Hotel de Bangkok</t>
+          <t>CLOUD on Saladaeng Hostel</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>โรงแรม</t>
+          <t>โฮสเทล/เกสต์เฮาส์</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>02-630-6401</t>
+          <t>02-029-9729</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="H27" t="n">
-        <v>2197</v>
+        <v>9</v>
       </c>
       <c r="I27" t="n">
-        <v>890</v>
+        <v>1120</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/DCUevV</t>
+          <t>https://hotels.cloudbeds.com/reservation/iGlZHg</t>
         </is>
       </c>
     </row>
@@ -6065,31 +6208,31 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sabai Sathorn Serviced Apartment</t>
+          <t>Pas Cher Hotel de Bangkok</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>เซอร์วิส อพาร์ตเมนต์</t>
+          <t>โรงแรม</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>02-267-3999</t>
+          <t>02-630-6401</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H28" t="n">
-        <v>2281</v>
+        <v>2197</v>
       </c>
       <c r="I28" t="n">
-        <v>1780</v>
+        <v>890</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/yqwDkx</t>
+          <t>https://hotels.cloudbeds.com/reservation/DCUevV</t>
         </is>
       </c>
     </row>
@@ -6106,31 +6249,31 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>The Cube Hostel Silom</t>
+          <t>Sabai Sathorn Serviced Apartment</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>โฮสเทล/เกสต์เฮาส์</t>
+          <t>เซอร์วิส อพาร์ตเมนต์</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>096-314-1481</t>
+          <t>02-267-3999</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="H29" t="n">
-        <v>1785</v>
+        <v>2281</v>
       </c>
       <c r="I29" t="n">
-        <v>700</v>
+        <v>1780</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/EWugHt</t>
+          <t>https://hotels.cloudbeds.com/reservation/yqwDkx</t>
         </is>
       </c>
     </row>
@@ -6142,12 +6285,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ปทุมวัน</t>
+          <t>บางรัก</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Happy Station Bangkok</t>
+          <t>The Cube Hostel Silom</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6157,18 +6300,21 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>064-545-2262</t>
+          <t>096-314-1481</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>9.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="H30" t="n">
-        <v>601</v>
+        <v>1785</v>
+      </c>
+      <c r="I30" t="n">
+        <v>700</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/fikDq8</t>
+          <t>https://hotels.cloudbeds.com/reservation/EWugHt</t>
         </is>
       </c>
     </row>
@@ -6185,31 +6331,28 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Happy3 Hotel</t>
+          <t>Happy Station Bangkok</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>โรงแรม</t>
+          <t>โฮสเทล/เกสต์เฮาส์</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>02-612-4799</t>
+          <t>064-545-2262</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>8.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H31" t="n">
-        <v>3890</v>
-      </c>
-      <c r="I31" t="n">
-        <v>1550</v>
+        <v>601</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/1cHXGt</t>
+          <t>https://hotels.cloudbeds.com/reservation/fikDq8</t>
         </is>
       </c>
     </row>
@@ -6226,31 +6369,31 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>House of Papa Bangkok Siam</t>
+          <t>Happy3 Hotel</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>โฮสเทล/เกสต์เฮาส์</t>
+          <t>โรงแรม</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>092-428-8264</t>
+          <t>02-612-4799</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>8.300000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="H32" t="n">
-        <v>935</v>
+        <v>3890</v>
       </c>
       <c r="I32" t="n">
-        <v>1150</v>
+        <v>1550</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/9zztFS</t>
+          <t>https://hotels.cloudbeds.com/reservation/1cHXGt</t>
         </is>
       </c>
     </row>
@@ -6267,31 +6410,31 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Roompini</t>
+          <t>House of Papa Bangkok Siam</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>บูทีค</t>
+          <t>โฮสเทล/เกสต์เฮาส์</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>061-016-7878</t>
+          <t>092-428-8264</t>
         </is>
       </c>
       <c r="G33" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="H33" t="n">
-        <v>138</v>
+        <v>935</v>
       </c>
       <c r="I33" t="n">
-        <v>1500</v>
+        <v>1150</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/lseUw6</t>
+          <t>https://hotels.cloudbeds.com/reservation/9zztFS</t>
         </is>
       </c>
     </row>
@@ -6308,31 +6451,31 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tamni</t>
+          <t>Roompini</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>โฮสเทล/เกสต์เฮาส์</t>
+          <t>บูทีค</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>063-932-2905</t>
+          <t>061-016-7878</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>9.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H34" t="n">
-        <v>2442</v>
+        <v>138</v>
       </c>
       <c r="I34" t="n">
-        <v>880</v>
+        <v>1500</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/IgoyOJ</t>
+          <t>https://hotels.cloudbeds.com/reservation/lseUw6</t>
         </is>
       </c>
     </row>
@@ -6344,12 +6487,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>พระนคร</t>
+          <t>ปทุมวัน</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chern Bangkok</t>
+          <t>Tamni</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -6359,21 +6502,21 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>02-621-1133</t>
+          <t>063-932-2905</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="H35" t="n">
-        <v>7235</v>
+        <v>2442</v>
       </c>
       <c r="I35" t="n">
-        <v>1250</v>
+        <v>880</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/sAIhvt</t>
+          <t>https://hotels.cloudbeds.com/reservation/IgoyOJ</t>
         </is>
       </c>
     </row>
@@ -6390,7 +6533,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Here Hostel</t>
+          <t>Chern Bangkok</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6400,21 +6543,21 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>090-987-7438</t>
+          <t>02-621-1133</t>
         </is>
       </c>
       <c r="G36" t="n">
         <v>8.4</v>
       </c>
       <c r="H36" t="n">
-        <v>2852</v>
+        <v>7235</v>
       </c>
       <c r="I36" t="n">
-        <v>880</v>
+        <v>1250</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/REBSPs</t>
+          <t>https://hotels.cloudbeds.com/reservation/sAIhvt</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6574,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Jam Hostel Bangkok</t>
+          <t>Here Hostel</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6441,21 +6584,21 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>02-282-3932</t>
+          <t>090-987-7438</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>9.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="H37" t="n">
-        <v>2778</v>
+        <v>2852</v>
       </c>
       <c r="I37" t="n">
-        <v>750</v>
+        <v>880</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/MlkqNX</t>
+          <t>https://hotels.cloudbeds.com/reservation/REBSPs</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6615,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Khao San Social Capsule Hostel</t>
+          <t>Jam Hostel Bangkok</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6482,18 +6625,21 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>091-027-8783</t>
+          <t>02-282-3932</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>9.1</v>
+        <v>9.699999999999999</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2778</v>
       </c>
       <c r="I38" t="n">
-        <v>1100</v>
+        <v>750</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/zgiCVH</t>
+          <t>https://hotels.cloudbeds.com/reservation/MlkqNX</t>
         </is>
       </c>
     </row>
@@ -6510,7 +6656,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Lost Inn BKK</t>
+          <t>Khao San Social Capsule Hostel</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6520,21 +6666,18 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>02-126-7901</t>
+          <t>091-027-8783</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="H39" t="n">
-        <v>971</v>
+        <v>9.1</v>
       </c>
       <c r="I39" t="n">
-        <v>900</v>
+        <v>1100</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/en/reservation/hu2DyZ</t>
+          <t>https://hotels.cloudbeds.com/reservation/zgiCVH</t>
         </is>
       </c>
     </row>
@@ -6551,7 +6694,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>NapPark Hostel</t>
+          <t>Lost Inn BKK</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6561,21 +6704,21 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>02-282-2324</t>
+          <t>02-126-7901</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>9.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="H40" t="n">
-        <v>9600</v>
+        <v>971</v>
       </c>
       <c r="I40" t="n">
-        <v>360</v>
+        <v>900</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/kN89VP</t>
+          <t>https://hotels.cloudbeds.com/en/reservation/hu2DyZ</t>
         </is>
       </c>
     </row>
@@ -6592,7 +6735,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Revolution Khaosan (by The Bliss)</t>
+          <t>NapPark Hostel</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6602,18 +6745,21 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>096-856-5360</t>
+          <t>02-282-2324</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H41" t="n">
-        <v>1592</v>
+        <v>9600</v>
+      </c>
+      <c r="I41" t="n">
+        <v>360</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/en/reservation/qPj3wK</t>
+          <t>https://hotels.cloudbeds.com/reservation/kN89VP</t>
         </is>
       </c>
     </row>
@@ -6630,31 +6776,28 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Siri Grand Bangkok Hotel</t>
+          <t>Revolution Khaosan (by The Bliss)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>โรงแรม</t>
+          <t>โฮสเทล/เกสต์เฮาส์</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>065-384-4660</t>
+          <t>096-856-5360</t>
         </is>
       </c>
       <c r="G42" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="H42" t="n">
-        <v>52</v>
-      </c>
-      <c r="I42" t="n">
-        <v>2400</v>
+        <v>1592</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/H8FTGQ</t>
+          <t>https://hotels.cloudbeds.com/en/reservation/qPj3wK</t>
         </is>
       </c>
     </row>
@@ -6671,31 +6814,31 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Suneta Hostel Khaosan</t>
+          <t>Siri Grand Bangkok Hotel</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>โฮสเทล/เกสต์เฮาส์</t>
+          <t>โรงแรม</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>061-101-6266</t>
+          <t>065-384-4660</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H43" t="n">
-        <v>1140</v>
+        <v>52</v>
       </c>
       <c r="I43" t="n">
-        <v>560</v>
+        <v>2400</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/en/reservation/RItaN7</t>
+          <t>https://hotels.cloudbeds.com/reservation/H8FTGQ</t>
         </is>
       </c>
     </row>
@@ -6712,7 +6855,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ti Thong Hostel</t>
+          <t>Suneta Hostel Khaosan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6722,21 +6865,21 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>064-001-6721</t>
+          <t>061-101-6266</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>8.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H44" t="n">
-        <v>639</v>
+        <v>1140</v>
       </c>
       <c r="I44" t="n">
-        <v>1100</v>
+        <v>560</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/en/reservation/AifE4v</t>
+          <t>https://hotels.cloudbeds.com/en/reservation/RItaN7</t>
         </is>
       </c>
     </row>
@@ -6748,12 +6891,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ราชเทวี</t>
+          <t>พระนคร</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Monument Stay</t>
+          <t>Ti Thong Hostel</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6763,15 +6906,21 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>064-742-4561</t>
+          <t>064-001-6721</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
+      </c>
+      <c r="H45" t="n">
+        <v>639</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1100</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/en/reservation/1GcujK</t>
+          <t>https://hotels.cloudbeds.com/en/reservation/AifE4v</t>
         </is>
       </c>
     </row>
@@ -6788,7 +6937,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Natee Hostel</t>
+          <t>Monument Stay</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6798,7 +6947,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>084-347-9920</t>
+          <t>064-742-4561</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6806,7 +6955,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/HVuqFl</t>
+          <t>https://hotels.cloudbeds.com/en/reservation/1GcujK</t>
         </is>
       </c>
     </row>
@@ -6823,7 +6972,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>The Victory View (adults only)</t>
+          <t>Natee Hostel</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6833,21 +6982,15 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>093-860-5914</t>
+          <t>084-347-9920</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="H47" t="n">
-        <v>619</v>
-      </c>
-      <c r="I47" t="n">
-        <v>700</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/en/reservation/QFq9Zv</t>
+          <t>https://hotels.cloudbeds.com/reservation/HVuqFl</t>
         </is>
       </c>
     </row>
@@ -6859,12 +7002,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>วัฒนา</t>
+          <t>ราชเทวี</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>3Howw Hostel @ Sukhumvit 21</t>
+          <t>The Victory View (adults only)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6874,18 +7017,21 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>099-909-6997</t>
+          <t>093-860-5914</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>7.7</v>
+        <v>8.6</v>
       </c>
       <c r="H48" t="n">
-        <v>2741</v>
+        <v>619</v>
+      </c>
+      <c r="I48" t="n">
+        <v>700</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/jABe3g</t>
+          <t>https://hotels.cloudbeds.com/en/reservation/QFq9Zv</t>
         </is>
       </c>
     </row>
@@ -6902,7 +7048,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Lamurr Sukhumvit 41</t>
+          <t>3Howw Hostel @ Sukhumvit 21</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6912,18 +7058,18 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>02-040-4653</t>
+          <t>099-909-6997</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>8.4</v>
+        <v>7.7</v>
       </c>
       <c r="H49" t="n">
-        <v>1129</v>
+        <v>2741</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/dBVH5M</t>
+          <t>https://hotels.cloudbeds.com/reservation/jABe3g</t>
         </is>
       </c>
     </row>
@@ -6940,22 +7086,28 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Narastay @ Phrom Phong</t>
+          <t>Lamurr Sukhumvit 41</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>เซอร์วิส อพาร์ตเมนต์</t>
+          <t>โฮสเทล/เกสต์เฮาส์</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>062-818-1865</t>
-        </is>
+          <t>02-040-4653</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1129</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/mQ8KAh</t>
+          <t>https://hotels.cloudbeds.com/reservation/dBVH5M</t>
         </is>
       </c>
     </row>
@@ -6972,26 +7124,28 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>StayAt Bedever Bangkok Hotel</t>
+          <t>Met A Space Pod @Phrom Phong</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>บูทีค</t>
+          <t>โฮสเทล/เกสต์เฮาส์</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>084 689 2264</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H51" t="n">
-        <v>61</v>
-      </c>
-      <c r="I51" t="n">
-        <v>730</v>
+        <v>252</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>https://us2.cloudbeds.com/reservation/z3rPaG</t>
+          <t>https://hotels.cloudbeds.com/reservation/rXdLyg</t>
         </is>
       </c>
     </row>
@@ -7003,36 +7157,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>สัมพันธวงศ์</t>
+          <t>วัฒนา</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Luk Hostel</t>
+          <t>Narastay @ Phrom Phong</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>โฮสเทล/เกสต์เฮาส์</t>
+          <t>เซอร์วิส อพาร์ตเมนต์</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>092-280-3385</t>
-        </is>
-      </c>
-      <c r="G52" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="H52" t="n">
-        <v>1774</v>
-      </c>
-      <c r="I52" t="n">
-        <v>880</v>
+          <t>062-818-1865</t>
+        </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/HlTUl3</t>
+          <t>https://hotels.cloudbeds.com/reservation/mQ8KAh</t>
         </is>
       </c>
     </row>
@@ -7044,38 +7189,115 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
+          <t>วัฒนา</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>StayAt Bedever Bangkok Hotel</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>บูทีค</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H53" t="n">
+        <v>61</v>
+      </c>
+      <c r="I53" t="n">
+        <v>730</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>https://us2.cloudbeds.com/reservation/z3rPaG</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>สัมพันธวงศ์</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Luk Hostel</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>โฮสเทล/เกสต์เฮาส์</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>092-280-3385</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="H54" t="n">
+        <v>1774</v>
+      </c>
+      <c r="I54" t="n">
+        <v>880</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>https://hotels.cloudbeds.com/reservation/HlTUl3</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
           <t>สาทร</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>Jasaen Stylish Boutique Hotel</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>บูทีค</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>02-675-9198</t>
         </is>
       </c>
-      <c r="G53" t="n">
+      <c r="G55" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="H53" t="n">
+      <c r="H55" t="n">
         <v>840</v>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>https://hotels.cloudbeds.com/reservation/JXh4be</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J53"/>
+  <autoFilter ref="A1:J55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7086,7 +7308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7734,34 +7956,28 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sib Kao</t>
+          <t>Met A Space Pod @Phrom Phong</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>โรงแรม</t>
+          <t>โฮสเทล/เกสต์เฮาส์</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>02-254-3200</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>3</v>
+          <t>084 689 2264</t>
+        </is>
       </c>
       <c r="G16" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>1082</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1190</v>
+        <v>252</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/LCLlYQ</t>
+          <t>https://hotels.cloudbeds.com/reservation/rXdLyg</t>
         </is>
       </c>
     </row>
@@ -7773,83 +7989,83 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>สัมพันธวงศ์</t>
+          <t>วัฒนา</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tiny Taladnoi Hostel</t>
+          <t>Sib Kao</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>โฮสเทล/เกสต์เฮาส์</t>
+          <t>โรงแรม</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>02-048-8515</t>
+          <t>02-254-3200</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G17" t="n">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="H17" t="n">
-        <v>565</v>
+        <v>1082</v>
       </c>
       <c r="I17" t="n">
-        <v>600</v>
+        <v>1190</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/hveMzn</t>
+          <t>https://hotels.cloudbeds.com/reservation/LCLlYQ</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ดีมาก 8-8.9</t>
+          <t>ดีเยี่ยม 9+</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>คลองเตย</t>
+          <t>สัมพันธวงศ์</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Arawana Regency Park Sukhumvit</t>
+          <t>Tiny Taladnoi Hostel</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>โรงแรม</t>
+          <t>โฮสเทล/เกสต์เฮาส์</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>02-259-7420</t>
+          <t>02-048-8515</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G18" t="n">
-        <v>8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>261</v>
+        <v>565</v>
       </c>
       <c r="I18" t="n">
-        <v>1400</v>
+        <v>600</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/IyqM8b</t>
+          <t>https://hotels.cloudbeds.com/reservation/hveMzn</t>
         </is>
       </c>
     </row>
@@ -7861,12 +8077,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>บางรัก</t>
+          <t>คลองเตย</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pas Cher Hotel de Bangkok</t>
+          <t>Arawana Regency Park Sukhumvit</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -7876,21 +8092,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>02-630-6401</t>
-        </is>
+          <t>02-259-7420</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>4</v>
       </c>
       <c r="G19" t="n">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="H19" t="n">
-        <v>2197</v>
+        <v>261</v>
       </c>
       <c r="I19" t="n">
-        <v>890</v>
+        <v>1400</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/DCUevV</t>
+          <t>https://hotels.cloudbeds.com/reservation/IyqM8b</t>
         </is>
       </c>
     </row>
@@ -7907,31 +8126,31 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sabai Sathorn Serviced Apartment</t>
+          <t>Pas Cher Hotel de Bangkok</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>เซอร์วิส อพาร์ตเมนต์</t>
+          <t>โรงแรม</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>02-267-3999</t>
+          <t>02-630-6401</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>2281</v>
+        <v>2197</v>
       </c>
       <c r="I20" t="n">
-        <v>1780</v>
+        <v>890</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/yqwDkx</t>
+          <t>https://hotels.cloudbeds.com/reservation/DCUevV</t>
         </is>
       </c>
     </row>
@@ -7948,31 +8167,31 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>The Cube Hostel Silom</t>
+          <t>Sabai Sathorn Serviced Apartment</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>โฮสเทล/เกสต์เฮาส์</t>
+          <t>เซอร์วิส อพาร์ตเมนต์</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>096-314-1481</t>
+          <t>02-267-3999</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="H21" t="n">
-        <v>1785</v>
+        <v>2281</v>
       </c>
       <c r="I21" t="n">
-        <v>700</v>
+        <v>1780</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/EWugHt</t>
+          <t>https://hotels.cloudbeds.com/reservation/yqwDkx</t>
         </is>
       </c>
     </row>
@@ -7984,36 +8203,36 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ปทุมวัน</t>
+          <t>บางรัก</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Happy3 Hotel</t>
+          <t>The Cube Hostel Silom</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>โรงแรม</t>
+          <t>โฮสเทล/เกสต์เฮาส์</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>02-612-4799</t>
+          <t>096-314-1481</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="H22" t="n">
-        <v>3890</v>
+        <v>1785</v>
       </c>
       <c r="I22" t="n">
-        <v>1550</v>
+        <v>700</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/1cHXGt</t>
+          <t>https://hotels.cloudbeds.com/reservation/EWugHt</t>
         </is>
       </c>
     </row>
@@ -8030,31 +8249,31 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>House of Papa Bangkok Siam</t>
+          <t>Happy3 Hotel</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>โฮสเทล/เกสต์เฮาส์</t>
+          <t>โรงแรม</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>092-428-8264</t>
+          <t>02-612-4799</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>8.300000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="H23" t="n">
-        <v>935</v>
+        <v>3890</v>
       </c>
       <c r="I23" t="n">
-        <v>1150</v>
+        <v>1550</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/9zztFS</t>
+          <t>https://hotels.cloudbeds.com/reservation/1cHXGt</t>
         </is>
       </c>
     </row>
@@ -8071,31 +8290,31 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Roompini</t>
+          <t>House of Papa Bangkok Siam</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>บูทีค</t>
+          <t>โฮสเทล/เกสต์เฮาส์</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>061-016-7878</t>
+          <t>092-428-8264</t>
         </is>
       </c>
       <c r="G24" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>138</v>
+        <v>935</v>
       </c>
       <c r="I24" t="n">
-        <v>1500</v>
+        <v>1150</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/lseUw6</t>
+          <t>https://hotels.cloudbeds.com/reservation/9zztFS</t>
         </is>
       </c>
     </row>
@@ -8107,36 +8326,36 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>พระนคร</t>
+          <t>ปทุมวัน</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chern Bangkok</t>
+          <t>Roompini</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>โฮสเทล/เกสต์เฮาส์</t>
+          <t>บูทีค</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>02-621-1133</t>
+          <t>061-016-7878</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>7235</v>
+        <v>138</v>
       </c>
       <c r="I25" t="n">
-        <v>1250</v>
+        <v>1500</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/sAIhvt</t>
+          <t>https://hotels.cloudbeds.com/reservation/lseUw6</t>
         </is>
       </c>
     </row>
@@ -8153,7 +8372,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Here Hostel</t>
+          <t>Chern Bangkok</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -8163,21 +8382,21 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>090-987-7438</t>
+          <t>02-621-1133</t>
         </is>
       </c>
       <c r="G26" t="n">
         <v>8.4</v>
       </c>
       <c r="H26" t="n">
-        <v>2852</v>
+        <v>7235</v>
       </c>
       <c r="I26" t="n">
-        <v>880</v>
+        <v>1250</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/REBSPs</t>
+          <t>https://hotels.cloudbeds.com/reservation/sAIhvt</t>
         </is>
       </c>
     </row>
@@ -8194,7 +8413,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Lost Inn BKK</t>
+          <t>Here Hostel</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -8204,21 +8423,21 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>02-126-7901</t>
+          <t>090-987-7438</t>
         </is>
       </c>
       <c r="G27" t="n">
         <v>8.4</v>
       </c>
       <c r="H27" t="n">
-        <v>971</v>
+        <v>2852</v>
       </c>
       <c r="I27" t="n">
-        <v>900</v>
+        <v>880</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/en/reservation/hu2DyZ</t>
+          <t>https://hotels.cloudbeds.com/reservation/REBSPs</t>
         </is>
       </c>
     </row>
@@ -8235,34 +8454,31 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Nanda Heritage Hotel</t>
+          <t>Lost Inn BKK</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>บูทีค</t>
+          <t>โฮสเทล/เกสต์เฮาส์</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>02-282-2900</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>3.5</v>
+          <t>02-126-7901</t>
+        </is>
       </c>
       <c r="G28" t="n">
         <v>8.4</v>
       </c>
       <c r="H28" t="n">
-        <v>2108</v>
+        <v>971</v>
       </c>
       <c r="I28" t="n">
-        <v>1100</v>
+        <v>900</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/K0i9sF</t>
+          <t>https://hotels.cloudbeds.com/en/reservation/hu2DyZ</t>
         </is>
       </c>
     </row>
@@ -8279,34 +8495,34 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Peace Land Khaosan</t>
+          <t>Nanda Heritage Hotel</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>โรงแรม</t>
+          <t>บูทีค</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>02-628-9090</t>
+          <t>02-282-2900</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>3.5</v>
       </c>
       <c r="G29" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="H29" t="n">
-        <v>48</v>
+        <v>2108</v>
       </c>
       <c r="I29" t="n">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/kSEVxf</t>
+          <t>https://hotels.cloudbeds.com/reservation/K0i9sF</t>
         </is>
       </c>
     </row>
@@ -8323,31 +8539,34 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Suneta Hostel Khaosan</t>
+          <t>Peace Land Khaosan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>โฮสเทล/เกสต์เฮาส์</t>
+          <t>โรงแรม</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>061-101-6266</t>
-        </is>
+          <t>02-628-9090</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>3.5</v>
       </c>
       <c r="G30" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="H30" t="n">
-        <v>1140</v>
+        <v>48</v>
       </c>
       <c r="I30" t="n">
-        <v>560</v>
+        <v>1200</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/en/reservation/RItaN7</t>
+          <t>https://hotels.cloudbeds.com/reservation/kSEVxf</t>
         </is>
       </c>
     </row>
@@ -8364,31 +8583,31 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>The Gravitique Hotel Khaosan</t>
+          <t>Suneta Hostel Khaosan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>บูทีค</t>
+          <t>โฮสเทล/เกสต์เฮาส์</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>02-121-4415</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>4</v>
+          <t>061-101-6266</t>
+        </is>
       </c>
       <c r="G31" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1140</v>
       </c>
       <c r="I31" t="n">
-        <v>2000</v>
+        <v>560</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/HGkMdX</t>
+          <t>https://hotels.cloudbeds.com/en/reservation/RItaN7</t>
         </is>
       </c>
     </row>
@@ -8405,31 +8624,31 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ti Thong Hostel</t>
+          <t>The Gravitique Hotel Khaosan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>โฮสเทล/เกสต์เฮาส์</t>
+          <t>บูทีค</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>064-001-6721</t>
-        </is>
+          <t>02-121-4415</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>4</v>
       </c>
       <c r="G32" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H32" t="n">
-        <v>639</v>
+        <v>8.9</v>
       </c>
       <c r="I32" t="n">
-        <v>1100</v>
+        <v>2000</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/en/reservation/AifE4v</t>
+          <t>https://hotels.cloudbeds.com/reservation/HGkMdX</t>
         </is>
       </c>
     </row>
@@ -8441,39 +8660,36 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ราชเทวี</t>
+          <t>พระนคร</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>4M Pratunam Hotel</t>
+          <t>Ti Thong Hostel</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>โรงแรม</t>
+          <t>โฮสเทล/เกสต์เฮาส์</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>02-251-5545</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>3</v>
+          <t>064-001-6721</t>
+        </is>
       </c>
       <c r="G33" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="H33" t="n">
-        <v>1190</v>
+        <v>639</v>
       </c>
       <c r="I33" t="n">
-        <v>760</v>
+        <v>1100</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/BJAq9T</t>
+          <t>https://hotels.cloudbeds.com/en/reservation/AifE4v</t>
         </is>
       </c>
     </row>
@@ -8490,25 +8706,34 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Monument Stay</t>
+          <t>4M Pratunam Hotel</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>โฮสเทล/เกสต์เฮาส์</t>
+          <t>โรงแรม</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>064-742-4561</t>
-        </is>
+          <t>02-251-5545</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>3</v>
       </c>
       <c r="G34" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1190</v>
+      </c>
+      <c r="I34" t="n">
+        <v>760</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/en/reservation/1GcujK</t>
+          <t>https://hotels.cloudbeds.com/reservation/BJAq9T</t>
         </is>
       </c>
     </row>
@@ -8525,7 +8750,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Natee Hostel</t>
+          <t>Hostel MovyLodge</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -8535,15 +8760,21 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>084-347-9920</t>
-        </is>
+          <t>097 745 4545</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>2</v>
       </c>
       <c r="G35" t="n">
         <v>8.800000000000001</v>
       </c>
+      <c r="H35" t="n">
+        <v>658</v>
+      </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/HVuqFl</t>
+          <t>https://hotels.cloudbeds.com/reservation/LIR7bX</t>
         </is>
       </c>
     </row>
@@ -8560,34 +8791,25 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spenza Hotel</t>
+          <t>Monument Stay</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>โรงแรม</t>
+          <t>โฮสเทล/เกสต์เฮาส์</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>02-251-5251</t>
-        </is>
-      </c>
-      <c r="F36" t="n">
-        <v>3</v>
+          <t>064-742-4561</t>
+        </is>
       </c>
       <c r="G36" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="H36" t="n">
-        <v>1926</v>
-      </c>
-      <c r="I36" t="n">
-        <v>910</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/m9POZF</t>
+          <t>https://hotels.cloudbeds.com/en/reservation/1GcujK</t>
         </is>
       </c>
     </row>
@@ -8604,7 +8826,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>The Victory View (adults only)</t>
+          <t>Natee Hostel</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -8614,21 +8836,15 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>093-860-5914</t>
+          <t>084-347-9920</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="H37" t="n">
-        <v>619</v>
-      </c>
-      <c r="I37" t="n">
-        <v>700</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/en/reservation/QFq9Zv</t>
+          <t>https://hotels.cloudbeds.com/reservation/HVuqFl</t>
         </is>
       </c>
     </row>
@@ -8645,7 +8861,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Yello Rooms Hotel Victory Monument</t>
+          <t>Spenza Hotel</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -8655,24 +8871,24 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>02-002-9428</t>
+          <t>02-251-5251</t>
         </is>
       </c>
       <c r="F38" t="n">
         <v>3</v>
       </c>
       <c r="G38" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="H38" t="n">
-        <v>906</v>
+        <v>1926</v>
       </c>
       <c r="I38" t="n">
-        <v>1500</v>
+        <v>910</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/zMkAEo</t>
+          <t>https://hotels.cloudbeds.com/reservation/m9POZF</t>
         </is>
       </c>
     </row>
@@ -8684,12 +8900,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>วัฒนา</t>
+          <t>ราชเทวี</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Lamurr Sukhumvit 41</t>
+          <t>The Victory View (adults only)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8699,18 +8915,21 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>02-040-4653</t>
+          <t>093-860-5914</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="H39" t="n">
-        <v>1129</v>
+        <v>619</v>
+      </c>
+      <c r="I39" t="n">
+        <v>700</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/dBVH5M</t>
+          <t>https://hotels.cloudbeds.com/en/reservation/QFq9Zv</t>
         </is>
       </c>
     </row>
@@ -8722,31 +8941,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>วัฒนา</t>
+          <t>ราชเทวี</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>StayAt Bedever Bangkok Hotel</t>
+          <t>Yello Rooms Hotel Victory Monument</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>บูทีค</t>
-        </is>
+          <t>โรงแรม</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>02-002-9428</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>3</v>
       </c>
       <c r="G40" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H40" t="n">
-        <v>61</v>
+        <v>906</v>
       </c>
       <c r="I40" t="n">
-        <v>730</v>
+        <v>1500</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>https://us2.cloudbeds.com/reservation/z3rPaG</t>
+          <t>https://hotels.cloudbeds.com/reservation/zMkAEo</t>
         </is>
       </c>
     </row>
@@ -8758,12 +8985,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>สัมพันธวงศ์</t>
+          <t>วัฒนา</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Luk Hostel</t>
+          <t>Lamurr Sukhumvit 41</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8773,21 +9000,18 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>092-280-3385</t>
+          <t>02-040-4653</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="H41" t="n">
-        <v>1774</v>
-      </c>
-      <c r="I41" t="n">
-        <v>880</v>
+        <v>1129</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/HlTUl3</t>
+          <t>https://hotels.cloudbeds.com/reservation/dBVH5M</t>
         </is>
       </c>
     </row>
@@ -8799,12 +9023,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>สาทร</t>
+          <t>วัฒนา</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Jasaen Stylish Boutique Hotel</t>
+          <t>StayAt Bedever Bangkok Hotel</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8812,20 +9036,18 @@
           <t>บูทีค</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>02-675-9198</t>
-        </is>
-      </c>
       <c r="G42" t="n">
-        <v>8.300000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H42" t="n">
-        <v>840</v>
+        <v>61</v>
+      </c>
+      <c r="I42" t="n">
+        <v>730</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/JXh4be</t>
+          <t>https://us2.cloudbeds.com/reservation/z3rPaG</t>
         </is>
       </c>
     </row>
@@ -8837,118 +9059,118 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>สาทร</t>
+          <t>สัมพันธวงศ์</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Urbana Sathorn</t>
+          <t>Luk Hostel</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>เซอร์วิส อพาร์ตเมนต์</t>
+          <t>โฮสเทล/เกสต์เฮาส์</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>02-227-9999</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v>5</v>
+          <t>092-280-3385</t>
+        </is>
       </c>
       <c r="G43" t="n">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H43" t="n">
-        <v>4554</v>
+        <v>1774</v>
       </c>
       <c r="I43" t="n">
-        <v>1900</v>
+        <v>880</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/kXbLpy</t>
+          <t>https://hotels.cloudbeds.com/reservation/HlTUl3</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ดี 7-7.9</t>
+          <t>ดีมาก 8-8.9</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>จตุจักร</t>
+          <t>สาทร</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bed to Bangkok</t>
+          <t>Jasaen Stylish Boutique Hotel</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>โฮสเทล/เกสต์เฮาส์</t>
+          <t>บูทีค</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>082-210-0268</t>
+          <t>02-675-9198</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>7.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H44" t="n">
-        <v>226</v>
+        <v>840</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/13e7WW</t>
+          <t>https://hotels.cloudbeds.com/reservation/JXh4be</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ดี 7-7.9</t>
+          <t>ดีมาก 8-8.9</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ดอนเมือง</t>
+          <t>สาทร</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweetloft Hotel Don Muang</t>
+          <t>Urbana Sathorn</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>โรงแรม</t>
+          <t>เซอร์วิส อพาร์ตเมนต์</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>080-060-7877</t>
+          <t>02-227-9999</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G45" t="n">
-        <v>7.6</v>
+        <v>8</v>
+      </c>
+      <c r="H45" t="n">
+        <v>4554</v>
       </c>
       <c r="I45" t="n">
-        <v>650</v>
+        <v>1900</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/je81zl</t>
+          <t>https://hotels.cloudbeds.com/reservation/kXbLpy</t>
         </is>
       </c>
     </row>
@@ -8960,39 +9182,33 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ดินแดง</t>
+          <t>จตุจักร</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>The Mini R Ratchada Hotel</t>
+          <t>Bed to Bangkok</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>โรงแรม</t>
+          <t>โฮสเทล/เกสต์เฮาส์</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>02-689-5173</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>3</v>
+          <t>082-210-0268</t>
+        </is>
       </c>
       <c r="G46" t="n">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="H46" t="n">
-        <v>390</v>
-      </c>
-      <c r="I46" t="n">
-        <v>1250</v>
+        <v>226</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/en/reservation/0TyYnZ</t>
+          <t>https://hotels.cloudbeds.com/reservation/13e7WW</t>
         </is>
       </c>
     </row>
@@ -9004,36 +9220,36 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>บางรัก</t>
+          <t>ดอนเมือง</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>BRB Hostel Bangkok Silom</t>
+          <t>Sweetloft Hotel Don Muang</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>โฮสเทล/เกสต์เฮาส์</t>
+          <t>โรงแรม</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>061-515-9898</t>
-        </is>
+          <t>080-060-7877</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>3</v>
       </c>
       <c r="G47" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="H47" t="n">
-        <v>1420</v>
+        <v>7.6</v>
       </c>
       <c r="I47" t="n">
-        <v>460</v>
+        <v>650</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/vhyeOS</t>
+          <t>https://hotels.cloudbeds.com/reservation/je81zl</t>
         </is>
       </c>
     </row>
@@ -9045,39 +9261,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>พระนคร</t>
+          <t>ดินแดง</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>OH Hostels - Bangkok</t>
+          <t>The Mini R Ratchada Hotel</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>โฮสเทล/เกสต์เฮาส์</t>
+          <t>โรงแรม</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>063-412-0779</t>
+          <t>02-689-5173</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G48" t="n">
         <v>7.7</v>
       </c>
       <c r="H48" t="n">
-        <v>1817</v>
+        <v>390</v>
       </c>
       <c r="I48" t="n">
-        <v>400</v>
+        <v>1250</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/fAz0pU</t>
+          <t>https://hotels.cloudbeds.com/en/reservation/0TyYnZ</t>
         </is>
       </c>
     </row>
@@ -9089,12 +9305,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>วัฒนา</t>
+          <t>บางรัก</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>3Howw Hostel @ Sukhumvit 21</t>
+          <t>BRB Hostel Bangkok Silom</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -9104,18 +9320,21 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>099-909-6997</t>
+          <t>061-515-9898</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="H49" t="n">
-        <v>2741</v>
+        <v>1420</v>
+      </c>
+      <c r="I49" t="n">
+        <v>460</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/jABe3g</t>
+          <t>https://hotels.cloudbeds.com/reservation/vhyeOS</t>
         </is>
       </c>
     </row>
@@ -9127,39 +9346,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>วัฒนา</t>
+          <t>พระนคร</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sakura Sky Residence</t>
+          <t>OH Hostels - Bangkok</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>โรงแรม</t>
+          <t>โฮสเทล/เกสต์เฮาส์</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>02-259-5999</t>
+          <t>063-412-0779</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G50" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="H50" t="n">
-        <v>412</v>
+        <v>1817</v>
       </c>
       <c r="I50" t="n">
-        <v>920</v>
+        <v>400</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/519d0O</t>
+          <t>https://hotels.cloudbeds.com/reservation/fAz0pU</t>
         </is>
       </c>
     </row>
@@ -9176,41 +9395,35 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>W 21 Hotel Bangkok</t>
+          <t>3Howw Hostel @ Sukhumvit 21</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>โรงแรม</t>
+          <t>โฮสเทล/เกสต์เฮาส์</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>02-661-6200</t>
-        </is>
-      </c>
-      <c r="F51" t="n">
-        <v>3</v>
+          <t>099-909-6997</t>
+        </is>
       </c>
       <c r="G51" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="H51" t="n">
-        <v>1548</v>
-      </c>
-      <c r="I51" t="n">
-        <v>1020</v>
+        <v>2741</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/3pn5ml</t>
+          <t>https://hotels.cloudbeds.com/reservation/jABe3g</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ต่ำกว่า 7</t>
+          <t>ดี 7-7.9</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -9220,7 +9433,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Thonglor Suites Hotel</t>
+          <t>Sakura Sky Residence</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -9230,61 +9443,149 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>02-001-2698</t>
+          <t>02-259-5999</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="G52" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="H52" t="n">
-        <v>73</v>
+        <v>412</v>
       </c>
       <c r="I52" t="n">
         <v>920</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/tN3wfD</t>
+          <t>https://hotels.cloudbeds.com/reservation/519d0O</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>ดี 7-7.9</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>วัฒนา</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>W 21 Hotel Bangkok</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>โรงแรม</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>02-661-6200</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>3</v>
+      </c>
+      <c r="G53" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H53" t="n">
+        <v>1548</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1020</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>https://hotels.cloudbeds.com/reservation/3pn5ml</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>ต่ำกว่า 7</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>วัฒนา</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Thonglor Suites Hotel</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>โรงแรม</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>02-001-2698</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G54" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H54" t="n">
+        <v>73</v>
+      </c>
+      <c r="I54" t="n">
+        <v>920</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>https://hotels.cloudbeds.com/reservation/tN3wfD</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>ไม่มีข้อมูล</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>วัฒนา</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>Narastay @ Phrom Phong</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>เซอร์วิส อพาร์ตเมนต์</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>062-818-1865</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>https://hotels.cloudbeds.com/reservation/mQ8KAh</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J53"/>
+  <autoFilter ref="A1:J55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9295,7 +9596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11289,7 +11590,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Monument Stay</t>
+          <t>Hostel MovyLodge</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -11299,15 +11600,21 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>064-742-4561</t>
-        </is>
+          <t>097 745 4545</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>2</v>
       </c>
       <c r="G48" t="n">
         <v>8.800000000000001</v>
       </c>
+      <c r="H48" t="n">
+        <v>658</v>
+      </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/en/reservation/1GcujK</t>
+          <t>https://hotels.cloudbeds.com/reservation/LIR7bX</t>
         </is>
       </c>
     </row>
@@ -11324,7 +11631,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Natee Hostel</t>
+          <t>Monument Stay</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -11334,7 +11641,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>084-347-9920</t>
+          <t>064-742-4561</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -11342,7 +11649,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/HVuqFl</t>
+          <t>https://hotels.cloudbeds.com/en/reservation/1GcujK</t>
         </is>
       </c>
     </row>
@@ -11354,12 +11661,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>วัฒนา</t>
+          <t>ราชเทวี</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>3Howw Hostel @ Sukhumvit 21</t>
+          <t>Natee Hostel</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -11369,18 +11676,15 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>099-909-6997</t>
+          <t>084-347-9920</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="H50" t="n">
-        <v>2741</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/jABe3g</t>
+          <t>https://hotels.cloudbeds.com/reservation/HVuqFl</t>
         </is>
       </c>
     </row>
@@ -11397,7 +11701,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Lamurr Sukhumvit 41</t>
+          <t>3Howw Hostel @ Sukhumvit 21</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -11407,18 +11711,18 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>02-040-4653</t>
+          <t>099-909-6997</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>8.4</v>
+        <v>7.7</v>
       </c>
       <c r="H51" t="n">
-        <v>1129</v>
+        <v>2741</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/dBVH5M</t>
+          <t>https://hotels.cloudbeds.com/reservation/jABe3g</t>
         </is>
       </c>
     </row>
@@ -11435,22 +11739,28 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Narastay @ Phrom Phong</t>
+          <t>Lamurr Sukhumvit 41</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>เซอร์วิส อพาร์ตเมนต์</t>
+          <t>โฮสเทล/เกสต์เฮาส์</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>062-818-1865</t>
-        </is>
+          <t>02-040-4653</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1129</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>https://hotels.cloudbeds.com/reservation/mQ8KAh</t>
+          <t>https://hotels.cloudbeds.com/reservation/dBVH5M</t>
         </is>
       </c>
     </row>
@@ -11462,38 +11772,108 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
+          <t>วัฒนา</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Met A Space Pod @Phrom Phong</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>โฮสเทล/เกสต์เฮาส์</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>084 689 2264</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H53" t="n">
+        <v>252</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>https://hotels.cloudbeds.com/reservation/rXdLyg</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>ไม่มีข้อมูล</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>วัฒนา</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Narastay @ Phrom Phong</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>เซอร์วิส อพาร์ตเมนต์</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>062-818-1865</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>https://hotels.cloudbeds.com/reservation/mQ8KAh</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ไม่มีข้อมูล</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
           <t>สาทร</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>Jasaen Stylish Boutique Hotel</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>บูทีค</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>02-675-9198</t>
         </is>
       </c>
-      <c r="G53" t="n">
+      <c r="G55" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="H53" t="n">
+      <c r="H55" t="n">
         <v>840</v>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>https://hotels.cloudbeds.com/reservation/JXh4be</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J53"/>
+  <autoFilter ref="A1:J55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>